--- a/data.mn/public/datasets/imported-vehicles-total.xlsx
+++ b/data.mn/public/datasets/imported-vehicles-total.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data (English)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data (Mongolian)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,18 +418,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>year</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Total Vehicles Imported</t>
+          <t>value</t>
         </is>
       </c>
     </row>
@@ -600,18 +600,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Он</t>
+          <t>он</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Нийт импортолсон тээврийн хэрэгсэл</t>
+          <t>утга</t>
         </is>
       </c>
     </row>
